--- a/results/01_pollution_assessment/PCA_Stressors/tables/chemical_descriptive_stats.xlsx
+++ b/results/01_pollution_assessment/PCA_Stressors/tables/chemical_descriptive_stats.xlsx
@@ -492,28 +492,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C2" t="n">
-        <v>5.77580976881725</v>
+        <v>5.947696446311747</v>
       </c>
       <c r="D2" t="n">
-        <v>2.885990351091968</v>
+        <v>2.776751299237309</v>
       </c>
       <c r="E2" t="n">
-        <v>49.97</v>
+        <v>46.69</v>
       </c>
       <c r="F2" t="n">
         <v>1.455</v>
       </c>
       <c r="G2" t="n">
-        <v>3.462</v>
+        <v>3.736</v>
       </c>
       <c r="H2" t="n">
-        <v>5.077650224785179</v>
+        <v>5.4</v>
       </c>
       <c r="I2" t="n">
-        <v>7.099143042493814</v>
+        <v>7.32775</v>
       </c>
       <c r="J2" t="n">
         <v>14.48817475379811</v>
@@ -529,28 +529,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C3" t="n">
-        <v>7815.466723552332</v>
+        <v>8272.556888634137</v>
       </c>
       <c r="D3" t="n">
-        <v>6680.858182915978</v>
+        <v>6259.239848247056</v>
       </c>
       <c r="E3" t="n">
-        <v>85.48</v>
+        <v>75.66</v>
       </c>
       <c r="F3" t="n">
         <v>1397</v>
       </c>
       <c r="G3" t="n">
-        <v>3659.671833108934</v>
+        <v>3974.25</v>
       </c>
       <c r="H3" t="n">
-        <v>4997.700708768216</v>
+        <v>5928.079705272265</v>
       </c>
       <c r="I3" t="n">
-        <v>9367.000000000004</v>
+        <v>10522.61304591838</v>
       </c>
       <c r="J3" t="n">
         <v>29257.98928474218</v>
@@ -566,28 +566,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C4" t="n">
-        <v>20.89645963242726</v>
+        <v>23.37250030437274</v>
       </c>
       <c r="D4" t="n">
-        <v>50.49971859763288</v>
+        <v>44.90404625805267</v>
       </c>
       <c r="E4" t="n">
-        <v>241.67</v>
+        <v>192.12</v>
       </c>
       <c r="F4" t="n">
         <v>2.097337453255524</v>
       </c>
       <c r="G4" t="n">
-        <v>6.815</v>
+        <v>7.410963825965163</v>
       </c>
       <c r="H4" t="n">
-        <v>11.11</v>
+        <v>14.74</v>
       </c>
       <c r="I4" t="n">
-        <v>19.02</v>
+        <v>25.98195773740457</v>
       </c>
       <c r="J4" t="n">
         <v>686.1206728442876</v>
@@ -603,34 +603,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C5" t="n">
-        <v>177.7570791642012</v>
+        <v>245.1027222248494</v>
       </c>
       <c r="D5" t="n">
-        <v>87.06495182955338</v>
+        <v>224.8148936440449</v>
       </c>
       <c r="E5" t="n">
-        <v>48.98</v>
+        <v>91.72</v>
       </c>
       <c r="F5" t="n">
         <v>33.16357581711508</v>
       </c>
       <c r="G5" t="n">
-        <v>114.5</v>
+        <v>130.3556463717394</v>
       </c>
       <c r="H5" t="n">
-        <v>160.0973338589046</v>
+        <v>195.165622172483</v>
       </c>
       <c r="I5" t="n">
-        <v>221.6642654762967</v>
+        <v>287.5174144147899</v>
       </c>
       <c r="J5" t="n">
-        <v>491.3454479634005</v>
+        <v>2100</v>
       </c>
       <c r="K5" t="n">
-        <v>458.1818721462854</v>
+        <v>2066.836424182885</v>
       </c>
     </row>
     <row r="6">
@@ -640,34 +640,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C6" t="n">
-        <v>15380.74253336919</v>
+        <v>19073.6978826076</v>
       </c>
       <c r="D6" t="n">
-        <v>10074.47293124698</v>
+        <v>17600.89516672427</v>
       </c>
       <c r="E6" t="n">
-        <v>65.5</v>
+        <v>92.28</v>
       </c>
       <c r="F6" t="n">
         <v>0.0001700000000000035</v>
       </c>
       <c r="G6" t="n">
-        <v>8336.999999999998</v>
+        <v>9583.249999999998</v>
       </c>
       <c r="H6" t="n">
-        <v>12640</v>
+        <v>14780.8657744594</v>
       </c>
       <c r="I6" t="n">
-        <v>20462.25278032151</v>
+        <v>22615.93647593306</v>
       </c>
       <c r="J6" t="n">
-        <v>61685.94707489108</v>
+        <v>143333.3333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>61685.94690489108</v>
+        <v>143333.3331633333</v>
       </c>
     </row>
     <row r="7">
@@ -677,34 +677,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C7" t="n">
-        <v>20.34200214078256</v>
+        <v>27.81988476316166</v>
       </c>
       <c r="D7" t="n">
-        <v>18.27185352332803</v>
+        <v>30.28783466469405</v>
       </c>
       <c r="E7" t="n">
-        <v>89.81999999999999</v>
+        <v>108.87</v>
       </c>
       <c r="F7" t="n">
         <v>2.22</v>
       </c>
       <c r="G7" t="n">
-        <v>8.815</v>
+        <v>10.0591152046063</v>
       </c>
       <c r="H7" t="n">
-        <v>13.84</v>
+        <v>18.30460925224131</v>
       </c>
       <c r="I7" t="n">
-        <v>26.02668553588768</v>
+        <v>32.6749370348861</v>
       </c>
       <c r="J7" t="n">
-        <v>121.6529340199169</v>
+        <v>260</v>
       </c>
       <c r="K7" t="n">
-        <v>119.4329340199169</v>
+        <v>257.78</v>
       </c>
     </row>
     <row r="8">
@@ -714,34 +714,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C8" t="n">
-        <v>26.667933820412</v>
+        <v>37.3432104736215</v>
       </c>
       <c r="D8" t="n">
-        <v>29.41844511858667</v>
+        <v>55.60377792539418</v>
       </c>
       <c r="E8" t="n">
-        <v>110.31</v>
+        <v>148.9</v>
       </c>
       <c r="F8" t="n">
         <v>0.000299999999999967</v>
       </c>
       <c r="G8" t="n">
-        <v>11.02</v>
+        <v>12.64287018588625</v>
       </c>
       <c r="H8" t="n">
-        <v>17.94</v>
+        <v>20.98295229513798</v>
       </c>
       <c r="I8" t="n">
-        <v>34.27</v>
+        <v>38.19447555293122</v>
       </c>
       <c r="J8" t="n">
-        <v>216.4</v>
+        <v>530</v>
       </c>
       <c r="K8" t="n">
-        <v>216.3997</v>
+        <v>529.9997</v>
       </c>
     </row>
     <row r="9">
@@ -751,34 +751,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C9" t="n">
-        <v>1120.814855502286</v>
+        <v>842.6033499052454</v>
       </c>
       <c r="D9" t="n">
-        <v>1632.884392231575</v>
+        <v>1495.615233764123</v>
       </c>
       <c r="E9" t="n">
-        <v>145.69</v>
+        <v>177.5</v>
       </c>
       <c r="F9" t="n">
-        <v>0.01493999999999995</v>
+        <v>0.001583037854187958</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1577999999999999</v>
+        <v>0.15</v>
       </c>
       <c r="H9" t="n">
-        <v>519.2267367629915</v>
+        <v>0.6517500000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>1603.214801791803</v>
+        <v>914.1382066878177</v>
       </c>
       <c r="J9" t="n">
         <v>6939.498155607749</v>
       </c>
       <c r="K9" t="n">
-        <v>6939.483215607749</v>
+        <v>6939.496572569895</v>
       </c>
     </row>
     <row r="10">
@@ -788,34 +788,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C10" t="n">
-        <v>9.988732259833323</v>
+        <v>34.10160270568834</v>
       </c>
       <c r="D10" t="n">
-        <v>19.22761787603767</v>
+        <v>106.7793750266695</v>
       </c>
       <c r="E10" t="n">
-        <v>192.49</v>
+        <v>313.12</v>
       </c>
       <c r="F10" t="n">
         <v>0.000119999999999898</v>
       </c>
       <c r="G10" t="n">
-        <v>1.162026034663228</v>
+        <v>1.8085</v>
       </c>
       <c r="H10" t="n">
-        <v>3.375</v>
+        <v>6.046132908939699</v>
       </c>
       <c r="I10" t="n">
-        <v>9.588999999999999</v>
+        <v>24.83330835891161</v>
       </c>
       <c r="J10" t="n">
-        <v>168.2</v>
+        <v>1100</v>
       </c>
       <c r="K10" t="n">
-        <v>168.19988</v>
+        <v>1099.99988</v>
       </c>
     </row>
     <row r="11">
@@ -825,34 +825,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C11" t="n">
-        <v>20.66826153286767</v>
+        <v>67.95209477936326</v>
       </c>
       <c r="D11" t="n">
-        <v>35.90893878671376</v>
+        <v>135.1299931838878</v>
       </c>
       <c r="E11" t="n">
-        <v>173.74</v>
+        <v>198.86</v>
       </c>
       <c r="F11" t="n">
         <v>0.0002560140000000821</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1784272309999999</v>
+        <v>0.2878048544999999</v>
       </c>
       <c r="H11" t="n">
-        <v>0.597018751</v>
+        <v>25.99000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>31.73000000000001</v>
+        <v>72.6375</v>
       </c>
       <c r="J11" t="n">
-        <v>331.9999999999998</v>
+        <v>970</v>
       </c>
       <c r="K11" t="n">
-        <v>331.9997439859998</v>
+        <v>969.999743986</v>
       </c>
     </row>
     <row r="12">
@@ -862,34 +862,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C12" t="n">
-        <v>72.19514599309889</v>
+        <v>54.31422919975037</v>
       </c>
       <c r="D12" t="n">
-        <v>197.3985145715824</v>
+        <v>173.85866045758</v>
       </c>
       <c r="E12" t="n">
-        <v>273.42</v>
+        <v>320.1</v>
       </c>
       <c r="F12" t="n">
-        <v>0.01071832147889817</v>
+        <v>0.0002197738964462024</v>
       </c>
       <c r="G12" t="n">
-        <v>1.816037551398685</v>
+        <v>0.2998121278883507</v>
       </c>
       <c r="H12" t="n">
-        <v>6.01308328824405</v>
+        <v>2.908231877629183</v>
       </c>
       <c r="I12" t="n">
-        <v>28.13898965717095</v>
+        <v>19.9315526951558</v>
       </c>
       <c r="J12" t="n">
         <v>1472.296600591508</v>
       </c>
       <c r="K12" t="n">
-        <v>1472.285882270029</v>
+        <v>1472.296380817612</v>
       </c>
     </row>
     <row r="13">
@@ -899,34 +899,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C13" t="n">
-        <v>0.951330223634218</v>
+        <v>1.334202159513286</v>
       </c>
       <c r="D13" t="n">
-        <v>1.002420375001714</v>
+        <v>2.355054368680273</v>
       </c>
       <c r="E13" t="n">
-        <v>105.37</v>
+        <v>176.51</v>
       </c>
       <c r="F13" t="n">
         <v>0.000140000000000029</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3079000000000001</v>
+        <v>0.3453122645458718</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5857514141456668</v>
+        <v>0.7163289174510845</v>
       </c>
       <c r="I13" t="n">
-        <v>1.243708471813451</v>
+        <v>1.426116154973743</v>
       </c>
       <c r="J13" t="n">
-        <v>7.408178572736873</v>
+        <v>28.66666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>7.408038572736873</v>
+        <v>28.66652666666667</v>
       </c>
     </row>
     <row r="14">
@@ -936,34 +936,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C14" t="n">
-        <v>1.05447546131788</v>
+        <v>0.7930512187518209</v>
       </c>
       <c r="D14" t="n">
-        <v>2.611112865203136</v>
+        <v>2.307907643356135</v>
       </c>
       <c r="E14" t="n">
-        <v>247.62</v>
+        <v>291.02</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0009999999999998899</v>
+        <v>1.083924561435989e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0.02600000000000002</v>
+        <v>0.00375</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2815108502726382</v>
+        <v>0.1300643120835535</v>
       </c>
       <c r="I14" t="n">
-        <v>0.785719318646829</v>
+        <v>0.5424670991159424</v>
       </c>
       <c r="J14" t="n">
         <v>17.836160871</v>
       </c>
       <c r="K14" t="n">
-        <v>17.835160871</v>
+        <v>17.83615003175439</v>
       </c>
     </row>
     <row r="15">
@@ -973,34 +973,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C15" t="n">
-        <v>2.195568957643701</v>
+        <v>1.651237056074065</v>
       </c>
       <c r="D15" t="n">
-        <v>5.023022208884167</v>
+        <v>4.454549801263775</v>
       </c>
       <c r="E15" t="n">
-        <v>228.78</v>
+        <v>269.77</v>
       </c>
       <c r="F15" t="n">
-        <v>0.002000000000000002</v>
+        <v>1.952544086622758e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2289487321132599</v>
+        <v>0.01</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5867891921827999</v>
+        <v>0.3342361455945899</v>
       </c>
       <c r="I15" t="n">
-        <v>2.140993292635482</v>
+        <v>1.180497522272005</v>
       </c>
       <c r="J15" t="n">
         <v>48.34018919413632</v>
       </c>
       <c r="K15" t="n">
-        <v>48.33818919413632</v>
+        <v>48.34016966869545</v>
       </c>
     </row>
     <row r="16">
@@ -1010,28 +1010,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C16" t="n">
-        <v>7.533046049621929</v>
+        <v>7.347131744106519</v>
       </c>
       <c r="D16" t="n">
-        <v>10.99095509732322</v>
+        <v>9.754369596078087</v>
       </c>
       <c r="E16" t="n">
-        <v>145.9</v>
+        <v>132.76</v>
       </c>
       <c r="F16" t="n">
         <v>9.999999999998899e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>1.771</v>
+        <v>2.04848866555157</v>
       </c>
       <c r="H16" t="n">
-        <v>2.908556769357288</v>
+        <v>3.573</v>
       </c>
       <c r="I16" t="n">
-        <v>5.654967322509089</v>
+        <v>7.074999999999999</v>
       </c>
       <c r="J16" t="n">
         <v>56.13496537433624</v>
@@ -1047,34 +1047,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>233</v>
+        <v>310</v>
       </c>
       <c r="C17" t="n">
-        <v>34912.93731479809</v>
+        <v>37535.80991295039</v>
       </c>
       <c r="D17" t="n">
-        <v>16139.90692504362</v>
+        <v>17074.81945324151</v>
       </c>
       <c r="E17" t="n">
-        <v>46.23</v>
+        <v>45.49</v>
       </c>
       <c r="F17" t="n">
         <v>4533.000000000001</v>
       </c>
       <c r="G17" t="n">
-        <v>22087.55196651153</v>
+        <v>25789.65373783997</v>
       </c>
       <c r="H17" t="n">
-        <v>34948.86911034861</v>
+        <v>37130.00000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>44830</v>
+        <v>46871.22213249248</v>
       </c>
       <c r="J17" t="n">
-        <v>84394.10564568819</v>
+        <v>99666.66666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>79861.10564568819</v>
+        <v>95133.66666666667</v>
       </c>
     </row>
   </sheetData>
